--- a/dados/base_dados/index_atasCMTT.xlsx
+++ b/dados/base_dados/index_atasCMTT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/giselebarbosa_prefeitura_sp_gov_br/Documents/Documentos/CMTT/Base_dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/giselebarbosa_prefeitura_sp_gov_br/Documents/Documentos/CMTT/Codigo/dados/base_dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="489" documentId="11_AD4D361C20488DEA4E38A0BA9CD873605ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5F35C92-1E69-47C4-B1A7-F3921722C160}"/>
+  <xr:revisionPtr revIDLastSave="510" documentId="11_AD4D361C20488DEA4E38A0BA9CD873605ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FED7E391-36DB-4CA4-8346-208B344C51A7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="13" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="275">
   <si>
     <t>Link: Link para reunião - Clique Aqui</t>
   </si>
@@ -838,6 +838,18 @@
   </si>
   <si>
     <t>Gravação Parte 1 e Parte 2</t>
+  </si>
+  <si>
+    <t>82ª Reunião Ordinária do Conselho Municipal de Trânsito e Transporte - CMTT</t>
+  </si>
+  <si>
+    <t>Data: 19/12/2025</t>
+  </si>
+  <si>
+    <t>Reunião Extraordinária do Conselho Municipal de Trânsito e Transporte - CMTT</t>
+  </si>
+  <si>
+    <t>Data: 02/01/2026</t>
   </si>
 </sst>
 </file>
@@ -893,7 +905,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -908,6 +920,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1193,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{943DB555-BD14-4E76-9761-A713D1CB5FE3}">
-  <dimension ref="A1:A573"/>
+  <dimension ref="A1:A587"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="128.42578125" style="5" customWidth="1"/>
@@ -3612,6 +3626,66 @@
     <row r="573" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A575" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A576" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A577" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A578" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A579" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A581" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A582" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A583" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A584" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A585" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A586" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A587" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3806,6 +3880,11 @@
     <hyperlink ref="A535" r:id="rId188" display="https://prefeitura.sp.gov.br/documents/d/mobilidade/77-reuniao-ordinaria-cmtt-28-02-2025-pdf" xr:uid="{9D88D43B-5448-465F-BBB9-A9DE0216DC10}"/>
     <hyperlink ref="A536" r:id="rId189" display="https://www.youtube.com/watch?v=p1aTS0khnwk" xr:uid="{7DD05FEA-68FD-4E43-A8A6-111EF9547254}"/>
     <hyperlink ref="A537" r:id="rId190" display="https://prefeitura.sp.gov.br/documents/d/mobilidade/apresentacao-vlt-plano-de-trabalho-28-02-2025-pdf" xr:uid="{69810EC0-28D9-463C-B479-A0E375596C35}"/>
+    <hyperlink ref="A578" r:id="rId191" display="https://prefeitura.sp.gov.br/documents/d/mobilidade/82-reuniao-ordinaria-do-cmtt-pdf" xr:uid="{621B72E0-5190-4ACD-9E77-EAF0F600BE1D}"/>
+    <hyperlink ref="A579" r:id="rId192" display="https://prefeitura.sp.gov.br/documents/d/mobilidade/balanco-faixa-azul-cmtt-rev1-pdf" xr:uid="{2886D79B-5EA6-4B23-AEAA-8F6E926DC7EE}"/>
+    <hyperlink ref="A585" r:id="rId193" display="https://teams.microsoft.com/meet/24202254047541?p=IekLSNheS8dbuYW3LQ" xr:uid="{099EDAA7-4482-4A16-A5EA-EF0EC5E50731}"/>
+    <hyperlink ref="A586" r:id="rId194" display="https://prefeitura.sp.gov.br/documents/d/mobilidade/reuniao-extraordinaria-do-cmtt-02-01-26-pdf" xr:uid="{F6E2B738-AC94-437D-88B2-F17218C48C5D}"/>
+    <hyperlink ref="A587" r:id="rId195" display="https://prefeitura.sp.gov.br/documents/d/mobilidade/20251230-apresentacao-cmtt-dez-25_-pdf" xr:uid="{D2CAE6E1-DF6C-4148-99F2-857C126F8368}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/dados/base_dados/index_atasCMTT.xlsx
+++ b/dados/base_dados/index_atasCMTT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/giselebarbosa_prefeitura_sp_gov_br/Documents/Documentos/CMTT/Codigo/dados/base_dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="510" documentId="11_AD4D361C20488DEA4E38A0BA9CD873605ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FED7E391-36DB-4CA4-8346-208B344C51A7}"/>
+  <xr:revisionPtr revIDLastSave="511" documentId="11_AD4D361C20488DEA4E38A0BA9CD873605ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{188E72FB-ECBD-436E-A41D-62597F6EF3BB}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25275" yWindow="960" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="13" r:id="rId1"/>
@@ -905,7 +905,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -920,8 +920,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -3629,62 +3628,62 @@
       </c>
     </row>
     <row r="575" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A575" s="6" t="s">
+      <c r="A575" s="5" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="576" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A576" s="6" t="s">
+      <c r="A576" s="5" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="577" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A577" s="6" t="s">
+      <c r="A577" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="578" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A578" s="7" t="s">
+      <c r="A578" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="579" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A579" s="7" t="s">
+      <c r="A579" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="581" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A581" s="6" t="s">
+      <c r="A581" s="5" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="582" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A582" s="6" t="s">
+      <c r="A582" s="5" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="583" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A583" s="6" t="s">
+      <c r="A583" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="584" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A584" s="6" t="s">
+      <c r="A584" s="5" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="585" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A585" s="7" t="s">
+      <c r="A585" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="586" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A586" s="7" t="s">
+      <c r="A586" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="587" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A587" s="7" t="s">
+      <c r="A587" s="6" t="s">
         <v>2</v>
       </c>
     </row>
